--- a/استيرا مستفيدين من الحركات.xlsx
+++ b/استيرا مستفيدين من الحركات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\Desktop\ضروري\حركات مستفيدين قديمة\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F960641-6C38-458B-BA8D-19E381F0C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25C2CB5-DBC6-43B4-A636-526D0D26E6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5052,6 +5052,7 @@
   <dimension ref="A1:C785"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/استيرا مستفيدين من الحركات.xlsx
+++ b/استيرا مستفيدين من الحركات.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C25C2CB5-DBC6-43B4-A636-526D0D26E6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE1E879-9093-4234-8A8A-6AC8969EAC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
